--- a/VerveStacks_IND_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_IND_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan10\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{49F30CC0-4C88-4E7F-A15B-879C680F9699}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB2F6732-C5A3-45CD-A191-B4245D2DC597}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3308" yWindow="3308" windowWidth="21600" windowHeight="12682" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AVA" sheetId="6" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="126">
   <si>
     <t>PSET_PN</t>
   </si>
@@ -410,6 +410,12 @@
   </si>
   <si>
     <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
+  </si>
+  <si>
+    <t>pset_pn</t>
+  </si>
+  <si>
+    <t>-*cofiring*</t>
   </si>
 </sst>
 </file>
@@ -2808,6 +2814,9 @@
         <v>66</v>
       </c>
       <c r="F49" t="s">
+        <v>124</v>
+      </c>
+      <c r="G49" t="s">
         <v>65</v>
       </c>
     </row>
@@ -2821,7 +2830,10 @@
       <c r="E50" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="F50" t="s">
+      <c r="F50" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="G50" t="s">
         <v>68</v>
       </c>
     </row>
@@ -2835,7 +2847,7 @@
       <c r="E51" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F51" t="s">
+      <c r="G51" t="s">
         <v>71</v>
       </c>
     </row>

--- a/VerveStacks_IND_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_IND_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -5,12 +5,12 @@
   <workbookPr updateLinks="never"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan10\SubRES_Tmpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_IND_grids_kan10\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB2F6732-C5A3-45CD-A191-B4245D2DC597}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B41B6005-56C2-4A93-9DA2-EF3B6364EE7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AVA" sheetId="6" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="127">
   <si>
     <t>PSET_PN</t>
   </si>
@@ -416,6 +416,9 @@
   </si>
   <si>
     <t>-*cofiring*</t>
+  </si>
+  <si>
+    <t>-EFF</t>
   </si>
 </sst>
 </file>
@@ -2635,6 +2638,9 @@
       <c r="G28" t="s">
         <v>5</v>
       </c>
+      <c r="H28" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="29" spans="3:24" x14ac:dyDescent="0.45">
       <c r="C29" t="s">
@@ -2656,6 +2662,9 @@
       </c>
       <c r="G30" s="1">
         <v>1</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="31" spans="3:24" x14ac:dyDescent="0.45">
